--- a/tame_output/ON/bt/strategyON_20240119.xlsx
+++ b/tame_output/ON/bt/strategyON_20240119.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1843</v>
+        <v>1844</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-01-17</t>
+          <t>2024-01-18</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -657,7 +657,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.9%</t>
+          <t>-11.5%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>-2.0%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>77.7%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,16 +768,16 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>59.4%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1843</v>
+        <v>1844</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-01-17</t>
+          <t>2024-01-18</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>64.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-5.2%</t>
+          <t>-5.1%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.1%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>31.3%</t>
+          <t>31.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1843</v>
+        <v>1844</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-01-17</t>
+          <t>2024-01-18</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>452.2%</t>
+          <t>451.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>1.7%</t>
+          <t>2.5%</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>31.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1089,11 +1089,11 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>58.5%</t>
+          <t>58.6%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1843</v>
+        <v>1844</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-01-17</t>
+          <t>2024-01-18</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-18.8%</t>
+          <t>-18.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>1.0%</t>
+          <t>1.1%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>51.8%</t>
+          <t>52.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1843</v>
+        <v>1844</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-01-17</t>
+          <t>2024-01-18</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>16.1%</t>
+          <t>16.0%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>1.4%</t>
         </is>
       </c>
     </row>
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1843</v>
+        <v>1844</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-01-17</t>
+          <t>2024-01-18</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>123.6%</t>
+          <t>123.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.9%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1846"/>
+  <dimension ref="A1:G1847"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44003,7 +44003,7 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.294483388684696</v>
+        <v>3.295507330201488</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
@@ -44019,6 +44019,29 @@
       </c>
       <c r="G1846" t="n">
         <v>4.466862599528316</v>
+      </c>
+    </row>
+    <row r="1847">
+      <c r="A1847" s="2" t="n">
+        <v>45309</v>
+      </c>
+      <c r="B1847" t="n">
+        <v>3.260795497384933</v>
+      </c>
+      <c r="C1847" t="n">
+        <v>3.117080449951029</v>
+      </c>
+      <c r="D1847" t="n">
+        <v>1.640585300295575</v>
+      </c>
+      <c r="E1847" t="n">
+        <v>3.772958145755513</v>
+      </c>
+      <c r="F1847" t="n">
+        <v>2.253724730484103</v>
+      </c>
+      <c r="G1847" t="n">
+        <v>4.469315288241491</v>
       </c>
     </row>
   </sheetData>
